--- a/worked_examples/AIHE-CASE07_remote_monitoring_cost_effectiveness_budget_impact_and_hta/workbook/xlsx/AIHE-CASE07_worked_example_and_template.xlsx
+++ b/worked_examples/AIHE-CASE07_remote_monitoring_cost_effectiveness_budget_impact_and_hta/workbook/xlsx/AIHE-CASE07_worked_example_and_template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R6a1d54d31b944ccf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="Rd9789b9fadd14bad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="Rb8001445650f4cfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R70cd4ad02d084e4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="Rf1d29d2d7f1a4104"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="R4a97ef7a87a6432c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="R79fab69949234b64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="Rb9f52a54a5554bad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -44,8 +44,14 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF303236"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -77,6 +83,16 @@
         <x:fgColor rgb="FFFFF3CD"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2230"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F0E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="36">
     <x:border/>
@@ -369,7 +385,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="101">
+  <x:cellXfs count="118">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -378,7 +394,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -386,7 +402,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -403,22 +419,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -435,22 +451,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -495,22 +511,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -525,22 +541,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -611,6 +627,53 @@
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -663,9 +726,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -774,25 +837,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Remote Monitoring: Cost-Effectiveness, Budget Impact, and HTA</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="102"/>
+      <x:c r="B2" s="102"/>
+      <x:c r="C2" s="102"/>
+      <x:c r="D2" s="102"/>
+      <x:c r="E2" s="102"/>
+      <x:c r="F2" s="102"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="21" t="str">
+      <x:c r="A4" s="104" t="str">
         <x:v>Example ID</x:v>
       </x:c>
       <x:c r="B4" s="42" t="str">
@@ -800,7 +863,7 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="22" t="str">
+      <x:c r="A5" s="106" t="str">
         <x:v>Chapter</x:v>
       </x:c>
       <x:c r="B5" s="43" t="str">
@@ -808,7 +871,7 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="22" t="str">
+      <x:c r="A6" s="106" t="str">
         <x:v>Decision question</x:v>
       </x:c>
       <x:c r="B6" s="43" t="str">
@@ -816,7 +879,7 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="22" t="str">
+      <x:c r="A7" s="106" t="str">
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B7" s="43" t="str">
@@ -824,7 +887,7 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="22" t="str">
+      <x:c r="A8" s="106" t="str">
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B8" s="43" t="str">
@@ -832,7 +895,7 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="22" t="str">
+      <x:c r="A9" s="106" t="str">
         <x:v>Release date</x:v>
       </x:c>
       <x:c r="B9" s="43" t="str">
@@ -840,7 +903,7 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="22" t="str">
+      <x:c r="A10" s="106" t="str">
         <x:v>How to use</x:v>
       </x:c>
       <x:c r="B10" s="43" t="str">
@@ -848,7 +911,7 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="22" t="str">
+      <x:c r="A11" s="106" t="str">
         <x:v>Related resources</x:v>
       </x:c>
       <x:c r="B11" s="43" t="str">
@@ -856,7 +919,7 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="23" t="str">
+      <x:c r="A12" s="108" t="str">
         <x:v>Data protection</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
@@ -883,31 +946,31 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Worked synthetic inputs and calculations</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
+      <x:c r="G1" s="102"/>
+      <x:c r="H1" s="102"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="112" t="str">
         <x:v>Parameter</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="113" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C3" s="59" t="str">
+      <x:c r="C3" s="114" t="str">
         <x:v>Unit</x:v>
       </x:c>
-      <x:c r="E3" s="57" t="str">
+      <x:c r="E3" s="112" t="str">
         <x:v>Calculation</x:v>
       </x:c>
-      <x:c r="F3" s="59" t="str">
+      <x:c r="F3" s="114" t="str">
         <x:v>Formula result</x:v>
       </x:c>
     </x:row>
@@ -1132,20 +1195,20 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Blank template - replace synthetic values with governed local evidence</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="112" t="str">
         <x:v>Parameter</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="113" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C3" s="59" t="str">
+      <x:c r="C3" s="114" t="str">
         <x:v>Unit</x:v>
       </x:c>
     </x:row>
@@ -1296,28 +1359,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Remote Monitoring: Cost-Effectiveness, Budget Impact, and HTA</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="102"/>
+      <x:c r="B2" s="102"/>
+      <x:c r="C2" s="102"/>
+      <x:c r="D2" s="102"/>
+      <x:c r="E2" s="102"/>
+      <x:c r="F2" s="102"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="57" t="str">
+      <x:c r="A4" s="112" t="str">
         <x:v>Reference metric</x:v>
       </x:c>
-      <x:c r="B4" s="59" t="str">
+      <x:c r="B4" s="114" t="str">
         <x:v>Synthetic result</x:v>
       </x:c>
     </x:row>
@@ -1346,66 +1409,66 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="89" t="str">
+      <x:c r="A9" s="115" t="str">
         <x:v>Worked interpretation</x:v>
       </x:c>
-      <x:c r="B9" s="89"/>
-      <x:c r="C9" s="89"/>
-      <x:c r="D9" s="89"/>
-      <x:c r="E9" s="89"/>
-      <x:c r="F9" s="89"/>
+      <x:c r="B9" s="115"/>
+      <x:c r="C9" s="115"/>
+      <x:c r="D9" s="115"/>
+      <x:c r="E9" s="115"/>
+      <x:c r="F9" s="115"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="94" t="str">
+      <x:c r="A10" s="116" t="str">
         <x:v>The incremental cost is 250 per patient and the modeled gain is 0.03 QALYs, producing an ICER of about 8,333 per QALY and positive net monetary benefit at a threshold of 50,000. The budget-impact result is different: implementation and uptake create a positive cash requirement. The recommended decision is conditional adoption with staged uptake, funded response capacity, reimbursement clarification, and monitoring of digital exclusion.</x:v>
       </x:c>
-      <x:c r="B10" s="94"/>
-      <x:c r="C10" s="94"/>
-      <x:c r="D10" s="94"/>
-      <x:c r="E10" s="94"/>
-      <x:c r="F10" s="94"/>
+      <x:c r="B10" s="116"/>
+      <x:c r="C10" s="116"/>
+      <x:c r="D10" s="116"/>
+      <x:c r="E10" s="116"/>
+      <x:c r="F10" s="116"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="94"/>
-      <x:c r="B11" s="94"/>
-      <x:c r="C11" s="94"/>
-      <x:c r="D11" s="94"/>
-      <x:c r="E11" s="94"/>
-      <x:c r="F11" s="94"/>
+      <x:c r="A11" s="116"/>
+      <x:c r="B11" s="116"/>
+      <x:c r="C11" s="116"/>
+      <x:c r="D11" s="116"/>
+      <x:c r="E11" s="116"/>
+      <x:c r="F11" s="116"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="94"/>
-      <x:c r="B12" s="94"/>
-      <x:c r="C12" s="94"/>
-      <x:c r="D12" s="94"/>
-      <x:c r="E12" s="94"/>
-      <x:c r="F12" s="94"/>
+      <x:c r="A12" s="116"/>
+      <x:c r="B12" s="116"/>
+      <x:c r="C12" s="116"/>
+      <x:c r="D12" s="116"/>
+      <x:c r="E12" s="116"/>
+      <x:c r="F12" s="116"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="94"/>
-      <x:c r="B13" s="94"/>
-      <x:c r="C13" s="94"/>
-      <x:c r="D13" s="94"/>
-      <x:c r="E13" s="94"/>
-      <x:c r="F13" s="94"/>
+      <x:c r="A13" s="116"/>
+      <x:c r="B13" s="116"/>
+      <x:c r="C13" s="116"/>
+      <x:c r="D13" s="116"/>
+      <x:c r="E13" s="116"/>
+      <x:c r="F13" s="116"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="94"/>
-      <x:c r="B14" s="94"/>
-      <x:c r="C14" s="94"/>
-      <x:c r="D14" s="94"/>
-      <x:c r="E14" s="94"/>
-      <x:c r="F14" s="94"/>
+      <x:c r="A14" s="116"/>
+      <x:c r="B14" s="116"/>
+      <x:c r="C14" s="116"/>
+      <x:c r="D14" s="116"/>
+      <x:c r="E14" s="116"/>
+      <x:c r="F14" s="116"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="100" t="str">
+      <x:c r="A16" s="117" t="str">
         <x:v>Interpret calculations with evidence quality, uncertainty, mandatory safeguards, implementation capacity, monitoring, and exit conditions.</x:v>
       </x:c>
-      <x:c r="B16" s="100"/>
-      <x:c r="C16" s="100"/>
-      <x:c r="D16" s="100"/>
-      <x:c r="E16" s="100"/>
-      <x:c r="F16" s="100"/>
+      <x:c r="B16" s="117"/>
+      <x:c r="C16" s="117"/>
+      <x:c r="D16" s="117"/>
+      <x:c r="E16" s="117"/>
+      <x:c r="F16" s="117"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
